--- a/data/metadata/spawning_season_wkmat07.xlsx
+++ b/data/metadata/spawning_season_wkmat07.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/fedma_dtu_dk/Documents/postdoc_dtu/length_at_maturity/data/extra/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/fedma_dtu_dk/Documents/postdoc_dtu/length_at_maturity/data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="8_{3EFBC03B-7CDF-C448-9106-43E3B8EA7F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4BC84E1-D407-0D4C-8DAB-AE304BBFDA23}"/>
+  <xr:revisionPtr revIDLastSave="284" documentId="8_{3EFBC03B-7CDF-C448-9106-43E3B8EA7F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92ADA603-DE9E-574A-9F6D-5CA4A0C89470}"/>
   <bookViews>
-    <workbookView xWindow="14540" yWindow="660" windowWidth="14560" windowHeight="18980" xr2:uid="{0AC15106-2965-0242-AB0B-32CDCB98883A}"/>
+    <workbookView xWindow="15160" yWindow="1000" windowWidth="14560" windowHeight="18980" xr2:uid="{0AC15106-2965-0242-AB0B-32CDCB98883A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="171">
   <si>
     <t>Species</t>
   </si>
@@ -113,9 +113,6 @@
     <t>Pollachius virens</t>
   </si>
   <si>
-    <t>Atlanto-Scandian herring</t>
-  </si>
-  <si>
     <t>Clupea harengus</t>
   </si>
   <si>
@@ -131,12 +128,6 @@
     <t>Anguilla anguilla</t>
   </si>
   <si>
-    <t>Northern prawn</t>
-  </si>
-  <si>
-    <t>Pandalus borealis</t>
-  </si>
-  <si>
     <t>Hake</t>
   </si>
   <si>
@@ -555,6 +546,9 @@
   </si>
   <si>
     <t>Scophthalmus maximus</t>
+  </si>
+  <si>
+    <t>Platichthys flesus </t>
   </si>
 </sst>
 </file>
@@ -989,7 +983,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1036,7 +1030,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1083,7 +1077,7 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1130,7 +1124,7 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1177,7 +1171,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1218,13 +1212,13 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1265,13 +1259,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1312,13 +1306,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1359,13 +1353,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1406,22 +1400,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1453,13 +1447,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1500,22 +1494,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1547,13 +1541,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
         <v>33</v>
       </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1594,13 +1588,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
         <v>35</v>
       </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1641,22 +1635,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
         <v>37</v>
       </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1688,13 +1682,13 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
         <v>39</v>
       </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1735,13 +1729,13 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1782,22 +1776,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1829,22 +1823,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
         <v>43</v>
       </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1876,22 +1870,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1909,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -1923,28 +1917,28 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1956,10 +1950,10 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -1970,22 +1964,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1994,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -2017,31 +2011,31 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -2064,37 +2058,37 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
         <v>80</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2111,19 +2105,19 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2138,16 +2132,16 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -2158,31 +2152,31 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2191,13 +2185,13 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -2205,13 +2199,13 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
         <v>52</v>
       </c>
-      <c r="B28" t="s">
-        <v>53</v>
-      </c>
       <c r="C28" t="s">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -2252,28 +2246,28 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2288,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -2299,19 +2293,19 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -2323,16 +2317,16 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -2346,19 +2340,19 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2370,22 +2364,22 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -2393,19 +2387,19 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2429,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -2440,19 +2434,19 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -2464,7 +2458,7 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -2487,37 +2481,37 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -2534,13 +2528,13 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2555,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>1</v>
@@ -2567,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -2581,13 +2575,13 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2617,7 +2611,7 @@
         <v>1</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -2628,13 +2622,13 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2661,10 +2655,10 @@
         <v>1</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -2675,13 +2669,13 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2690,22 +2684,22 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -2722,28 +2716,28 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2769,13 +2763,13 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -2787,7 +2781,7 @@
         <v>1</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2816,37 +2810,37 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
         <v>81</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2863,13 +2857,13 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
         <v>43</v>
       </c>
-      <c r="B42" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" t="s">
-        <v>84</v>
+      <c r="C42">
+        <v>4</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2884,16 +2878,16 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2910,13 +2904,13 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43">
-        <v>4</v>
+        <v>169</v>
+      </c>
+      <c r="C43" t="s">
+        <v>81</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2931,16 +2925,16 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2957,13 +2951,13 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>172</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2972,45 +2966,45 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
-      </c>
-      <c r="C45" t="s">
-        <v>75</v>
+        <v>97</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -3025,16 +3019,16 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
         <v>1</v>
@@ -3043,86 +3037,86 @@
         <v>1</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47">
-        <v>4</v>
+        <v>62</v>
+      </c>
+      <c r="C47" t="s">
+        <v>81</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3137,21 +3131,21 @@
         <v>0</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" t="s">
         <v>64</v>
       </c>
-      <c r="B48" t="s">
-        <v>65</v>
-      </c>
       <c r="C48" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -3160,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -3172,13 +3166,13 @@
         <v>1</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -3192,13 +3186,13 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" t="s">
-        <v>85</v>
+        <v>64</v>
+      </c>
+      <c r="C49">
+        <v>8</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -3219,13 +3213,13 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -3239,22 +3233,22 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50">
-        <v>8</v>
+        <v>16</v>
+      </c>
+      <c r="C50" t="s">
+        <v>93</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -3263,7 +3257,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3281,21 +3275,21 @@
         <v>0</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -3328,21 +3322,21 @@
         <v>0</v>
       </c>
       <c r="O51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -3375,21 +3369,21 @@
         <v>0</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3422,21 +3416,21 @@
         <v>0</v>
       </c>
       <c r="O53">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B54" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C54" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -3451,7 +3445,7 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3469,18 +3463,18 @@
         <v>0</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3501,7 +3495,7 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55">
         <v>0</v>
@@ -3516,18 +3510,18 @@
         <v>0</v>
       </c>
       <c r="O55">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C56" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3545,36 +3539,36 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="C57" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3586,10 +3580,10 @@
         <v>1</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3601,36 +3595,36 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>100</v>
+      </c>
+      <c r="B58" t="s">
         <v>101</v>
       </c>
-      <c r="B58" t="s">
-        <v>102</v>
-      </c>
       <c r="C58" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -3662,25 +3656,25 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="B59" t="s">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="C59" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -3709,16 +3703,16 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -3730,7 +3724,7 @@
         <v>1</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3745,24 +3739,24 @@
         <v>0</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="C61" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3774,10 +3768,10 @@
         <v>1</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3792,24 +3786,24 @@
         <v>0</v>
       </c>
       <c r="M61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>104</v>
+      </c>
+      <c r="B62" t="s">
         <v>105</v>
       </c>
-      <c r="B62" t="s">
-        <v>106</v>
-      </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3850,13 +3844,13 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="B63" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="C63" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3868,13 +3862,13 @@
         <v>1</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -3897,16 +3891,16 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="C64" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -3944,16 +3938,16 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>108</v>
+      </c>
+      <c r="B65" t="s">
         <v>109</v>
       </c>
-      <c r="B65" t="s">
-        <v>110</v>
-      </c>
       <c r="C65" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -3991,22 +3985,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>110</v>
+      </c>
+      <c r="B66" t="s">
         <v>111</v>
       </c>
-      <c r="B66" t="s">
-        <v>112</v>
-      </c>
       <c r="C66" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -4018,7 +4012,7 @@
         <v>1</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -4038,13 +4032,13 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B67" t="s">
         <v>113</v>
       </c>
-      <c r="B67" t="s">
-        <v>114</v>
-      </c>
       <c r="C67" t="s">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -4053,19 +4047,19 @@
         <v>0</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -4085,19 +4079,19 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>114</v>
+      </c>
+      <c r="B68" t="s">
         <v>115</v>
       </c>
-      <c r="B68" t="s">
-        <v>116</v>
-      </c>
       <c r="C68" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -4106,10 +4100,10 @@
         <v>1</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4132,13 +4126,13 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>116</v>
+      </c>
+      <c r="B69" t="s">
         <v>117</v>
       </c>
-      <c r="B69" t="s">
-        <v>118</v>
-      </c>
       <c r="C69" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4156,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4168,10 +4162,10 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -4179,16 +4173,16 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>118</v>
+      </c>
+      <c r="B70" t="s">
         <v>119</v>
       </c>
-      <c r="B70" t="s">
-        <v>120</v>
-      </c>
       <c r="C70" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -4197,22 +4191,22 @@
         <v>1</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70">
         <v>1</v>
@@ -4226,25 +4220,25 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>120</v>
+      </c>
+      <c r="B71" t="s">
         <v>121</v>
       </c>
-      <c r="B71" t="s">
-        <v>122</v>
-      </c>
       <c r="C71" t="s">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -4265,7 +4259,7 @@
         <v>1</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4273,22 +4267,22 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="B72" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="C72" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -4297,19 +4291,19 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N72">
         <v>0</v>
@@ -4320,13 +4314,13 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B73" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C73" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -4367,28 +4361,28 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="B74" t="s">
-        <v>65</v>
-      </c>
-      <c r="C74" t="s">
-        <v>134</v>
+        <v>123</v>
+      </c>
+      <c r="C74">
+        <v>10</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -4414,34 +4408,34 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B75" t="s">
-        <v>126</v>
-      </c>
-      <c r="C75">
-        <v>10</v>
+        <v>133</v>
+      </c>
+      <c r="C75" t="s">
+        <v>134</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75">
         <v>0</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75">
         <v>0</v>
@@ -4450,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75">
         <v>0</v>
@@ -4467,7 +4461,7 @@
         <v>136</v>
       </c>
       <c r="C76" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -4476,7 +4470,7 @@
         <v>1</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -4508,19 +4502,19 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="B77" t="s">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -4529,13 +4523,13 @@
         <v>0</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -4544,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N77">
         <v>0</v>
@@ -4555,13 +4549,13 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -4602,13 +4596,13 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
-      </c>
-      <c r="C79" t="s">
-        <v>140</v>
+        <v>139</v>
+      </c>
+      <c r="C79">
+        <v>10</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -4649,13 +4643,13 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="B80" t="s">
-        <v>142</v>
-      </c>
-      <c r="C80">
-        <v>10</v>
+        <v>97</v>
+      </c>
+      <c r="C80" t="s">
+        <v>124</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -4696,13 +4690,13 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="B81" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="C81" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -4714,22 +4708,22 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81">
         <v>0</v>
@@ -4743,13 +4737,13 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>142</v>
+      </c>
+      <c r="B82" t="s">
         <v>143</v>
       </c>
-      <c r="B82" t="s">
-        <v>144</v>
-      </c>
-      <c r="C82" t="s">
-        <v>94</v>
+      <c r="C82">
+        <v>10</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -4761,22 +4755,22 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82">
         <v>0</v>
@@ -4790,13 +4784,13 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>144</v>
+      </c>
+      <c r="B83" t="s">
         <v>145</v>
       </c>
-      <c r="B83" t="s">
-        <v>146</v>
-      </c>
-      <c r="C83">
-        <v>10</v>
+      <c r="C83" t="s">
+        <v>124</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -4837,13 +4831,13 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="B84" t="s">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="C84" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -4884,13 +4878,13 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
-      </c>
-      <c r="C85" t="s">
-        <v>127</v>
+        <v>147</v>
+      </c>
+      <c r="C85">
+        <v>10</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -4931,13 +4925,13 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
+        <v>148</v>
+      </c>
+      <c r="B86" t="s">
         <v>149</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>150</v>
-      </c>
-      <c r="C86">
-        <v>10</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -4984,7 +4978,7 @@
         <v>152</v>
       </c>
       <c r="C87" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -5025,13 +5019,13 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>153</v>
+      </c>
+      <c r="B88" t="s">
         <v>154</v>
       </c>
-      <c r="B88" t="s">
-        <v>155</v>
-      </c>
       <c r="C88" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -5040,10 +5034,10 @@
         <v>0</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -5072,13 +5066,13 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>155</v>
+      </c>
+      <c r="B89" t="s">
         <v>156</v>
       </c>
-      <c r="B89" t="s">
-        <v>157</v>
-      </c>
       <c r="C89" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -5087,10 +5081,10 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -5119,13 +5113,13 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>157</v>
+      </c>
+      <c r="B90" t="s">
         <v>158</v>
       </c>
-      <c r="B90" t="s">
-        <v>159</v>
-      </c>
       <c r="C90" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -5166,13 +5160,13 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>159</v>
+      </c>
+      <c r="B91" t="s">
         <v>160</v>
       </c>
-      <c r="B91" t="s">
-        <v>161</v>
-      </c>
       <c r="C91" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -5213,13 +5207,13 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>161</v>
+      </c>
+      <c r="B92" t="s">
         <v>162</v>
       </c>
-      <c r="B92" t="s">
-        <v>163</v>
-      </c>
       <c r="C92" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -5260,13 +5254,13 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>164</v>
+        <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>165</v>
+        <v>68</v>
       </c>
       <c r="C93" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -5293,13 +5287,13 @@
         <v>0</v>
       </c>
       <c r="L93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -5307,13 +5301,13 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="C94" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -5325,13 +5319,13 @@
         <v>0</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5340,13 +5334,13 @@
         <v>0</v>
       </c>
       <c r="L94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94">
         <v>0</v>
